--- a/1A_2_3_4_merge.xlsx
+++ b/1A_2_3_4_merge.xlsx
@@ -2997,7 +2997,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>silence/noise</t>
+          <t>unknown_dialogue</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -3044,7 +3044,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>silence/noise</t>
+          <t>unknown_dialogue</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -3091,7 +3091,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>silence/noise</t>
+          <t>unknown_dialogue</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -3138,7 +3138,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>silence/noise</t>
+          <t>unknown_dialogue</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -4313,7 +4313,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>silence/noise</t>
+          <t>music</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -4360,7 +4360,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>silence/noise</t>
+          <t>music</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -4407,7 +4407,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>silence/noise</t>
+          <t>music</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -4454,7 +4454,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>silence/noise</t>
+          <t>music</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -5817,7 +5817,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>silence/noise</t>
+          <t>unknown_dialogue</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -5864,7 +5864,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>silence/noise</t>
+          <t>unknown_dialogue</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -5911,7 +5911,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>silence/noise</t>
+          <t>unknown_dialogue</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -5958,7 +5958,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>silence/noise</t>
+          <t>unknown_dialogue</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -7321,7 +7321,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>silence/noise</t>
+          <t>dialogue</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -7368,7 +7368,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>silence/noise</t>
+          <t>dialogue</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -7415,7 +7415,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>silence/noise</t>
+          <t>dialogue</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -7462,7 +7462,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>silence/noise</t>
+          <t>dialogue</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -11645,7 +11645,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>silence/noise</t>
+          <t>music</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -11692,7 +11692,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>silence/noise</t>
+          <t>music</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -11739,7 +11739,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>silence/noise</t>
+          <t>music</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -11786,7 +11786,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>silence/noise</t>
+          <t>music</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -12773,7 +12773,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>unknown_dialogue</t>
+          <t>silence/noise</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -12820,7 +12820,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>unknown_dialogue</t>
+          <t>silence/noise</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -12867,7 +12867,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>unknown_dialogue</t>
+          <t>silence/noise</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -12914,7 +12914,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>unknown_dialogue</t>
+          <t>silence/noise</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -13337,7 +13337,7 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>music</t>
+          <t>silence/noise</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -13384,7 +13384,7 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>music</t>
+          <t>silence/noise</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -13431,7 +13431,7 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>music</t>
+          <t>silence/noise</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -13478,7 +13478,7 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>music</t>
+          <t>silence/noise</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -13525,7 +13525,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>silence/noise</t>
+          <t>dialogue</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -13572,7 +13572,7 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>silence/noise</t>
+          <t>dialogue</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -13619,7 +13619,7 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>silence/noise</t>
+          <t>dialogue</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -13666,7 +13666,7 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>silence/noise</t>
+          <t>dialogue</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -15593,7 +15593,7 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>music</t>
+          <t>dialogue</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
@@ -15640,7 +15640,7 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>music</t>
+          <t>dialogue</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
@@ -15687,7 +15687,7 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>music</t>
+          <t>dialogue</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
@@ -15734,7 +15734,7 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>music</t>
+          <t>dialogue</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
@@ -18413,7 +18413,7 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>silence/noise</t>
+          <t>music</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
@@ -18460,7 +18460,7 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>silence/noise</t>
+          <t>music</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
@@ -18507,7 +18507,7 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>silence/noise</t>
+          <t>music</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
@@ -18554,7 +18554,7 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>silence/noise</t>
+          <t>music</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
@@ -21421,7 +21421,7 @@
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>dialogue</t>
+          <t>music</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
@@ -21468,7 +21468,7 @@
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>dialogue</t>
+          <t>music</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
@@ -21515,7 +21515,7 @@
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>dialogue</t>
+          <t>music</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
@@ -21562,7 +21562,7 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>dialogue</t>
+          <t>music</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
